--- a/Output Data Tables/AFAT Outputs/Aggregated Tables/2020/Airline_Cumulative_Financial_Statistics_2020.xlsx
+++ b/Output Data Tables/AFAT Outputs/Aggregated Tables/2020/Airline_Cumulative_Financial_Statistics_2020.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="44">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -178,7 +190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -204,49 +216,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1404,48 +1416,248 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>68722203780</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.19969999999999999</v>
+      </c>
+      <c r="D25" s="0">
+        <v>261.10000000000002</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="F25" s="0">
+        <v>432.01999999999998</v>
+      </c>
+      <c r="G25" s="0">
+        <v>37638800350</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0.1094</v>
+      </c>
+      <c r="I25" s="0">
+        <v>143</v>
+      </c>
+      <c r="J25" s="0">
+        <v>0.18290000000000001</v>
+      </c>
+      <c r="K25" s="0">
+        <v>236.61000000000001</v>
+      </c>
+      <c r="L25" s="0">
+        <v>214030</v>
+      </c>
+      <c r="M25" s="0">
+        <v>1608084</v>
+      </c>
+      <c r="N25" s="0">
+        <v>140944</v>
+      </c>
+      <c r="O25" s="0">
+        <v>175858</v>
+      </c>
+      <c r="P25" s="0">
+        <v>11.41</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>26584311740</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.1477</v>
+      </c>
+      <c r="D26" s="0">
+        <v>133.43000000000001</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="F26" s="0">
+        <v>261.47000000000003</v>
+      </c>
+      <c r="G26" s="0">
+        <v>15023256570</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0.083500000000000005</v>
+      </c>
+      <c r="I26" s="0">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="J26" s="0">
+        <v>0.156</v>
+      </c>
+      <c r="K26" s="0">
+        <v>147.75999999999999</v>
+      </c>
+      <c r="L26" s="0">
+        <v>89927</v>
+      </c>
+      <c r="M26" s="0">
+        <v>2001483</v>
+      </c>
+      <c r="N26" s="0">
+        <v>147416</v>
+      </c>
+      <c r="O26" s="0">
+        <v>167061</v>
+      </c>
+      <c r="P26" s="0">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>6068371240</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.098000000000000004</v>
+      </c>
+      <c r="D27" s="0">
+        <v>97.75</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.1479</v>
+      </c>
+      <c r="F27" s="0">
+        <v>150.44</v>
+      </c>
+      <c r="G27" s="0">
+        <v>4076002810</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0.065799999999999997</v>
+      </c>
+      <c r="I27" s="0">
+        <v>65.659999999999997</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0.099400000000000002</v>
+      </c>
+      <c r="K27" s="0">
+        <v>101.05</v>
+      </c>
+      <c r="L27" s="0">
+        <v>19710</v>
+      </c>
+      <c r="M27" s="0">
+        <v>3142287</v>
+      </c>
+      <c r="N27" s="0">
+        <v>101314</v>
+      </c>
+      <c r="O27" s="0">
+        <v>206799</v>
+      </c>
+      <c r="P27" s="0">
+        <v>31.02</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>7224473320</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.12180000000000001</v>
+      </c>
+      <c r="D28" s="0">
+        <v>60.490000000000002</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="F28" s="0">
+        <v>106.59999999999999</v>
+      </c>
+      <c r="G28" s="0">
+        <v>6143677020</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0.10349999999999999</v>
+      </c>
+      <c r="I28" s="0">
+        <v>51.439999999999998</v>
+      </c>
+      <c r="J28" s="0">
+        <v>0.1769</v>
+      </c>
+      <c r="K28" s="0">
+        <v>90.650000000000006</v>
+      </c>
+      <c r="L28" s="0">
+        <v>48703</v>
+      </c>
+      <c r="M28" s="0">
+        <v>1218272</v>
+      </c>
+      <c r="N28" s="0">
+        <v>68042</v>
+      </c>
+      <c r="O28" s="0">
+        <v>126146</v>
+      </c>
+      <c r="P28" s="0">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>108599360080</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>0.16830000000000001</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>168.63999999999999</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>0.28739999999999999</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>294.42000000000002</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>62881736750</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>0.0974</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>97.650000000000006</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>0.16639999999999999</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>170.47999999999999</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>372370</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>1733313</v>
       </c>
-      <c r="N25" s="0">
+      <c r="N29" s="0">
         <v>130874</v>
       </c>
-      <c r="O25" s="0">
+      <c r="O29" s="0">
         <v>168869</v>
       </c>
-      <c r="P25" s="0">
+      <c r="P29" s="0">
         <v>13.24</v>
       </c>
     </row>
